--- a/Containerization and DevOps/Lab/.attendance and proxies/MID VIVA B1 21 feb morning lab Attendance.xlsx
+++ b/Containerization and DevOps/Lab/.attendance and proxies/MID VIVA B1 21 feb morning lab Attendance.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Sheet1!$A$10:$M$41</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Sheet1!$A$10:$M$42</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="98">
   <si>
     <t xml:space="preserve">Brand</t>
   </si>
@@ -364,7 +364,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -387,6 +387,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF81D41A"/>
         <bgColor rgb="FF969696"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF800080"/>
+        <bgColor rgb="FF800080"/>
       </patternFill>
     </fill>
   </fills>
@@ -431,32 +437,40 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -469,7 +483,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="6">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -488,7 +502,23 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF800080"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -680,1140 +710,1164 @@
   <sheetPr filterMode="true">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="17.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="23.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="10.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="21.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="9.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="10.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="15.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="16.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="15.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="16.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="17.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="23.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="10.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="21.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="9.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="10.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="15.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="16.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="15.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="16.71"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
+      <c r="A9" s="4"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G10" s="5" t="n">
+      <c r="G10" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="H10" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I10" s="5" t="s">
+      <c r="I10" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="J10" s="5" t="s">
+      <c r="J10" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="K10" s="5" t="s">
+      <c r="K10" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="L10" s="5" t="s">
+      <c r="L10" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="M10" s="5" t="s">
+      <c r="M10" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" s="0" t="s">
+      <c r="A11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="E11" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="G11" s="0" t="n">
+      <c r="D11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" s="1" t="n">
         <v>90</v>
       </c>
-      <c r="I11" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="J11" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="K11" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="L11" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="M11" s="0" t="s">
+      <c r="I11" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M11" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" s="0" t="s">
+      <c r="A12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="E12" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="I12" s="0" t="s">
+      <c r="D12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I12" s="1" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13" s="0" t="s">
+      <c r="A13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D13" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="E13" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="G13" s="0" t="n">
+      <c r="D13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G13" s="1" t="n">
         <v>90</v>
       </c>
-      <c r="I13" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="J13" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="K13" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="L13" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="M13" s="0" t="s">
+      <c r="I13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M13" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="B14" s="0" t="s">
+      <c r="A14" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D14" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="E14" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="G14" s="0" t="n">
+      <c r="D14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G14" s="1" t="n">
         <v>90</v>
       </c>
-      <c r="I14" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="J14" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="K14" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="L14" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="M14" s="0" t="s">
+      <c r="I14" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M14" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" s="0" t="s">
+      <c r="A15" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D15" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="E15" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="G15" s="0" t="n">
+      <c r="D15" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G15" s="1" t="n">
         <v>80</v>
       </c>
-      <c r="I15" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="J15" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="K15" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="L15" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="M15" s="0" t="s">
+      <c r="I15" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M15" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="B16" s="0" t="s">
+      <c r="A16" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="D16" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="E16" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="G16" s="0" t="n">
+      <c r="D16" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G16" s="1" t="n">
         <v>75</v>
       </c>
-      <c r="I16" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="J16" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="K16" s="0" t="s">
+      <c r="I16" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K16" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="L16" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="M16" s="0" t="s">
+      <c r="L16" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M16" s="1" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="B17" s="0" t="s">
+      <c r="A17" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C17" s="0" t="s">
+      <c r="C17" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D17" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="E17" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="I17" s="0" t="s">
+      <c r="D17" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I17" s="1" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="B18" s="0" t="s">
+      <c r="A18" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D18" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="E18" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="G18" s="0" t="n">
+      <c r="D18" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G18" s="1" t="n">
         <v>75</v>
       </c>
-      <c r="I18" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="J18" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="K18" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="L18" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="M18" s="0" t="s">
+      <c r="I18" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M18" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="B19" s="0" t="s">
+      <c r="A19" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D19" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="E19" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="G19" s="0" t="n">
+      <c r="D19" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G19" s="1" t="n">
         <v>85</v>
       </c>
-      <c r="I19" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="J19" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="K19" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="L19" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="M19" s="0" t="s">
+      <c r="I19" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M19" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="B20" s="0" t="s">
+      <c r="A20" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="D20" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="E20" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="G20" s="0" t="n">
+      <c r="D20" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G20" s="1" t="n">
         <v>90</v>
       </c>
-      <c r="I20" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="J20" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="K20" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="L20" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="M20" s="0" t="s">
+      <c r="I20" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M20" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21" s="0" t="s">
+      <c r="A21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="D21" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="E21" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="G21" s="0" t="n">
+      <c r="D21" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G21" s="1" t="n">
         <v>85</v>
       </c>
-      <c r="I21" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="J21" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="K21" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="L21" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="M21" s="0" t="s">
+      <c r="I21" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M21" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="B22" s="0" t="s">
+      <c r="A22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="D22" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="E22" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="G22" s="0" t="n">
+      <c r="D22" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G22" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="I22" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="J22" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="K22" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="L22" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="M22" s="0" t="s">
+      <c r="I22" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M22" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="B23" s="0" t="s">
+      <c r="A23" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="D23" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="E23" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="G23" s="0" t="n">
+      <c r="D23" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G23" s="1" t="n">
         <v>75</v>
       </c>
-      <c r="I23" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="J23" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="K23" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="L23" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="M23" s="0" t="s">
+      <c r="I23" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M23" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="B24" s="0" t="s">
+      <c r="A24" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="D24" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="E24" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="G24" s="0" t="n">
+      <c r="D24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G24" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="I24" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="J24" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="K24" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="L24" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="M24" s="0" t="s">
+      <c r="I24" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M24" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="B25" s="0" t="s">
+      <c r="A25" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="D25" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="E25" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="G25" s="0" t="n">
+      <c r="D25" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G25" s="1" t="n">
         <v>85</v>
       </c>
-      <c r="I25" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="J25" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="K25" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="L25" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="M25" s="0" t="s">
+      <c r="I25" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M25" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="B26" s="0" t="s">
+      <c r="A26" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="D26" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="E26" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="G26" s="0" t="n">
+      <c r="D26" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G26" s="1" t="n">
         <v>85</v>
       </c>
-      <c r="I26" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="J26" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="K26" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="L26" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="M26" s="0" t="s">
+      <c r="I26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M26" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="B27" s="0" t="s">
+      <c r="A27" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="D27" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="E27" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="G27" s="0" t="n">
+      <c r="D27" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G27" s="1" t="n">
         <v>80</v>
       </c>
-      <c r="I27" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="J27" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="K27" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="L27" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="M27" s="0" t="s">
+      <c r="I27" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M27" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="B28" s="0" t="s">
+      <c r="A28" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="D28" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="E28" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="G28" s="0" t="n">
+      <c r="D28" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G28" s="1" t="n">
         <v>80</v>
       </c>
-      <c r="I28" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="J28" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="K28" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="L28" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="M28" s="0" t="s">
+      <c r="I28" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M28" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="B29" s="0" t="s">
+      <c r="A29" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C29" s="0" t="s">
+      <c r="C29" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="D29" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="E29" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="I29" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="J29" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="K29" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="L29" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="M29" s="0" t="s">
+      <c r="D29" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G29" s="0"/>
+      <c r="I29" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M29" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="B30" s="0" t="s">
+      <c r="A30" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C30" s="0" t="s">
+      <c r="C30" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="D30" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="E30" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="I30" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="J30" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="K30" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="L30" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="M30" s="0" t="s">
+      <c r="D30" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G30" s="1" t="n">
+        <v>80</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M30" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="B31" s="0" t="s">
+      <c r="A31" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="C31" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D31" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="E31" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="G31" s="0" t="n">
+      <c r="D31" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G31" s="1" t="n">
         <v>85</v>
       </c>
-      <c r="I31" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="J31" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="K31" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="L31" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="M31" s="0" t="s">
+      <c r="I31" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M31" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="B32" s="0" t="s">
+      <c r="A32" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="C32" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="D32" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="E32" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="G32" s="0" t="n">
+      <c r="D32" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G32" s="1" t="n">
         <v>85</v>
       </c>
-      <c r="I32" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="J32" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="K32" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="L32" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="M32" s="0" t="s">
+      <c r="I32" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M32" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="B33" s="0" t="s">
+      <c r="A33" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C33" s="0" t="s">
+      <c r="C33" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="D33" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="E33" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="I33" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="J33" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="K33" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="L33" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="M33" s="0" t="s">
+      <c r="D33" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M33" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="B34" s="0" t="s">
+      <c r="A34" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C34" s="0" t="s">
+      <c r="C34" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="D34" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="E34" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="I34" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="J34" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="K34" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="L34" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="M34" s="0" t="s">
+      <c r="D34" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M34" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="B35" s="0" t="s">
+      <c r="A35" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C35" s="6" t="s">
+      <c r="C35" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="D35" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="E35" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="G35" s="0" t="n">
+      <c r="D35" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G35" s="1" t="n">
         <v>85</v>
       </c>
-      <c r="I35" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="J35" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="K35" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="L35" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="M35" s="0" t="s">
+      <c r="I35" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M35" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="B36" s="0" t="s">
+      <c r="A36" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C36" s="0" t="s">
+      <c r="C36" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="D36" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="E36" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="I36" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="J36" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="K36" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="L36" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="M36" s="0" t="s">
+      <c r="D36" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G36" s="1" t="n">
+        <v>75</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M36" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="B37" s="0" t="s">
+      <c r="A37" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C37" s="0" t="s">
+      <c r="C37" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D37" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="E37" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="I37" s="0" t="s">
+      <c r="D37" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I37" s="1" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="B38" s="0" t="s">
+      <c r="A38" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C38" s="0" t="s">
+      <c r="C38" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D38" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="E38" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="I38" s="0" t="s">
+      <c r="D38" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I38" s="1" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="B39" s="0" t="s">
+      <c r="A39" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C39" s="0" t="s">
+      <c r="C39" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="D39" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="E39" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="I39" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="J39" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="K39" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="L39" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="M39" s="0" t="s">
+      <c r="D39" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G39" s="1" t="n">
+        <v>75</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M39" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="B40" s="0" t="s">
+      <c r="A40" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C40" s="0" t="s">
+      <c r="C40" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="D40" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="E40" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="I40" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="J40" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="K40" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="L40" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="M40" s="0" t="s">
+      <c r="D40" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G40" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M40" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="B41" s="0" t="s">
+      <c r="A41" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C41" s="0" t="s">
+      <c r="C41" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="D41" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="E41" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="I41" s="0" t="s">
+      <c r="D41" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I41" s="1" t="s">
         <v>38</v>
       </c>
     </row>
+    <row r="42" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C42" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="G42" s="1" t="n">
+        <v>85</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A10:M41">
+  <autoFilter ref="A10:M42">
     <filterColumn colId="8">
       <filters>
         <filter val="P"/>
